--- a/source_data/workbooks/Source_Data_ED_Fig8.xlsx
+++ b/source_data/workbooks/Source_Data_ED_Fig8.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="63">
   <si>
     <t>figure_panel</t>
   </si>
@@ -167,6 +167,9 @@
     <t>uncertainty_method</t>
   </si>
   <si>
+    <t>system_description</t>
+  </si>
+  <si>
     <t>Extended Data 8b</t>
   </si>
   <si>
@@ -176,6 +179,24 @@
     <t>SEA-AD held-out</t>
   </si>
   <si>
+    <t>Reactive fraction</t>
+  </si>
+  <si>
+    <t>Reactive/astrogl. ratio 35µm</t>
+  </si>
+  <si>
+    <t>Peripyramidal react. 35µm</t>
+  </si>
+  <si>
+    <t>partial_pearson_r</t>
+  </si>
+  <si>
+    <t>donors</t>
+  </si>
+  <si>
+    <t>SD across 100 repeated 80% donor subsamples</t>
+  </si>
+  <si>
     <t>Bulk reactive-astrocyte fraction</t>
   </si>
   <si>
@@ -183,15 +204,6 @@
   </si>
   <si>
     <t>Peripyramidal astrocyte-lineage reactivity, 35 um</t>
-  </si>
-  <si>
-    <t>partial_pearson_r</t>
-  </si>
-  <si>
-    <t>donors</t>
-  </si>
-  <si>
-    <t>SD across 100 repeated 80% donor subsamples</t>
   </si>
 </sst>
 </file>
@@ -921,14 +933,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="55.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -945,9 +957,10 @@
     <col min="22" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="19.7109375" customWidth="1"/>
     <col min="25" max="25" width="45.7109375" customWidth="1"/>
+    <col min="26" max="26" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1023,28 +1036,31 @@
       <c r="Y1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>34</v>
@@ -1083,30 +1099,33 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>59</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>34</v>
@@ -1145,30 +1164,33 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>59</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4">
         <v>34</v>
@@ -1207,30 +1229,33 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>59</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5">
         <v>34</v>
@@ -1269,30 +1294,33 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>59</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6">
         <v>34</v>
@@ -1331,30 +1359,33 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
       </c>
       <c r="H7">
         <v>34</v>
@@ -1393,7 +1424,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
